--- a/docs/bobcat-dash-BOM.xlsx
+++ b/docs/bobcat-dash-BOM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$5:$K$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$5:$K$120</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BOM'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3450,7 +3450,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>CHARGING: Delco 10SI 3-wire alternator (docs/wiring-schematic.jpg, section 7)</t>
+          <t>CYLINDER HEAD TEMPS + PARKING BRAKE (breakout board rev 3.0 AUX, breakout-board/cht-board): README, CHT / Parking brake</t>
         </is>
       </c>
       <c r="B88" s="5" t="n"/>
@@ -3473,27 +3473,27 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Rectifier diode</t>
+          <t>CHT + Parking Brake board</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>1N4001, 1 A 50 V</t>
+          <t>87 x 46 mm, blue, 2 layers</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>1N4001</t>
+          <t>PCBWay, breakout-board/cht-board/fab/cht-board-gerbers.zip</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Sch. 7</t>
+          <t>cht-board README</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>In the terminal 1 (excite) wire, band toward the alternator: stops the running alternator back-feeding the key circuit (engine run-on, dash never sees key-off)</t>
+          <t>Parts on the board: cht-board/fab/cht-board-bom.csv (sockets, PC817, LED, 1N4148, 22k, 43k, Micro-Fit, Phoenix)</t>
         </is>
       </c>
       <c r="H89" s="9" t="n"/>
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Resistor 47 Ω</t>
+          <t>CHT thermocouple</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>5 W wirewound</t>
+          <t>Type K, ungrounded, 18 mm ring, flexible stem, male mini K plug</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>The Sensor Connection CHT-FS-072-06-18-K-MP (or -120- / custom 144 in)</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Sch. 7</t>
+          <t>README: CHT</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>In series with the diode: ~0.25 A with the key on and the engine stopped, like the charge lamp it replaces. Use the alternator maker's value if they give one</t>
+          <t>One per cylinder (start with one). Under the spark plug, ring for 18 mm plugs (Champion D-16J)</t>
         </is>
       </c>
       <c r="H90" s="9" t="n"/>
@@ -3553,27 +3553,27 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Fusible link or circuit breaker</t>
+          <t>Thermocouple amplifier module</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Rated for the alternator (e.g. 60 A)</t>
+          <t>MCP9601, I2C, Type K, cold-junction compensated</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Adafruit 5165</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Sch. 7</t>
+          <t>cht-board README</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>On the BAT stud wire, near the battery end. 8 AWG wire (10 AWG for 45 A units)</t>
+          <t>One per thermocouple, in the CHT board's socket for that cylinder; leave its address jumpers open</t>
         </is>
       </c>
       <c r="H91" s="9" t="n"/>
@@ -3585,48 +3585,100 @@
       <c r="K91" s="12" t="n"/>
     </row>
     <row r="92">
-      <c r="G92" s="13" t="inlineStr">
-        <is>
-          <t>Subtotal — Charging: Delco 10Si 3-Wire Alternator</t>
-        </is>
-      </c>
-      <c r="I92" s="14">
-        <f>SUM(I89:I91)</f>
-        <v/>
-      </c>
+      <c r="A92" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Type K extension wire</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>KX, 20-24 AWG, FEP or fibreglass, stainless braid near the exhaust</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Omega EXTT-K-24 or similar</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>README: CHT</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>Length to reach the e-box. Never plain copper wire</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="n"/>
+      <c r="I92" s="10">
+        <f>B92*H92</f>
+        <v/>
+      </c>
+      <c r="J92" s="11" t="n"/>
+      <c r="K92" s="12" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>WIRING + ENCLOSURE</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
+      <c r="A93" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Mini Type K connector pair</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Female jack + male plug, Type K alloy contacts (yellow)</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Omega SMPW-K-F + SMPW-K-M or similar</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>README: CHT</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Extension ends; or a panel-mount mini K jack on the e-box wall</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="10">
+        <f>B93*H93</f>
+        <v/>
+      </c>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Enclosure</t>
+          <t>M2.5 standoff + screws</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>IP65+, fits Pi + interface boards</t>
+          <t>11 mm, brass</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -3636,12 +3688,12 @@
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cht-board README</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Vibration-mount it</t>
+          <t>Two per MCP9601 module</t>
         </is>
       </c>
       <c r="H94" s="9" t="n"/>
@@ -3654,34 +3706,34 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Prototype board</t>
+          <t>Micro-Fit 3.0 dual-row housings (pair)</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Perfboard / stripboard</t>
+          <t>2 x 3, latching</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Molex 43025-0600 (x2)</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cht-board README</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Only if hand-wiring instead of the breakout board</t>
+          <t>AUX cable: breakout board J18 to CHT board J1, pin 1 to pin 1</t>
         </is>
       </c>
       <c r="H95" s="9" t="n"/>
@@ -3694,34 +3746,34 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Automotive wire</t>
+          <t>Micro-Fit 3.0 crimp pins</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>18 AWG TXL/GXL, several colors</t>
+          <t>Female, 20-24 AWG</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Molex 43030-0007</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cht-board README</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Lot</t>
+          <t>AUX cable, both ends</t>
         </is>
       </c>
       <c r="H96" s="9" t="n"/>
@@ -3734,34 +3786,34 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B97" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Sealed connectors</t>
+          <t>Parking brake switch</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Deutsch DT or Weatherpack assortment</t>
+          <t>Sealed (IP67) roller-lever microswitch, closes when the brake is set, factory pigtail</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>e.g. Honeywell V15W series or similar</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>README: Parking brake</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Avoid loose Dupont jumpers on the machine</t>
+          <t>Mount on the handle; Deutsch DT 2-pin at the handle; to the CHT board's PARK BRAKE plug</t>
         </is>
       </c>
       <c r="H97" s="9" t="n"/>
@@ -3773,84 +3825,32 @@
       <c r="K97" s="12" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="B98" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>Screw terminal blocks</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>PCB 5 mm pitch assortment</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>Field wiring into the enclosure</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="n"/>
-      <c r="I98" s="10">
-        <f>B98*H98</f>
-        <v/>
-      </c>
-      <c r="J98" s="11" t="n"/>
-      <c r="K98" s="12" t="n"/>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>Subtotal — Cylinder Head Temps + Parking Brake</t>
+        </is>
+      </c>
+      <c r="I98" s="14">
+        <f>SUM(I89:I97)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="B99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>Heat-shrink + terminals</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Assortment</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="10">
-        <f>B99*H99</f>
-        <v/>
-      </c>
-      <c r="J99" s="11" t="n"/>
-      <c r="K99" s="12" t="n"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CHARGING: Delco 10SI 3-wire alternator (docs/wiring-schematic.jpg, section 7)</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="5" t="n"/>
+      <c r="K99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -3861,27 +3861,27 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Display mount</t>
+          <t>Rectifier diode</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>RAM-style ball mount or bracket</t>
+          <t>1N4001, 1 A 50 V</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1N4001</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sch. 7</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>With vibration damping</t>
+          <t>In the terminal 1 (excite) wire, band toward the alternator: stops the running alternator back-feeding the key circuit (engine run-on, dash never sees key-off)</t>
         </is>
       </c>
       <c r="H100" s="9" t="n"/>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Standoffs</t>
+          <t>Resistor 47 Ω</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>M2.5 nylon/brass set</t>
+          <t>5 W wirewound</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sch. 7</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Mount the Pi and the plug-in modules</t>
+          <t>In series with the diode: ~0.25 A with the key on and the engine stopped, like the charge lamp it replaces. Use the alternator maker's value if they give one</t>
         </is>
       </c>
       <c r="H101" s="9" t="n"/>
@@ -3937,16 +3937,16 @@
         <v>76</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>M3 standoff + screws</t>
+          <t>Fusible link or circuit breaker</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>10 mm or taller, all the same height</t>
+          <t>Rated for the alternator (e.g. 60 A)</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Board README</t>
+          <t>Sch. 7</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Breakout board mounting: 4 corners, 4 mid-sides, 1 centre (drilling template)</t>
+          <t>On the BAT stud wire, near the battery end. 8 AWG wire (10 AWG for 45 A units)</t>
         </is>
       </c>
       <c r="H102" s="9" t="n"/>
@@ -3975,18 +3975,18 @@
     <row r="103">
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Subtotal — Wiring + Enclosure</t>
+          <t>Subtotal — Charging: Delco 10Si 3-Wire Alternator</t>
         </is>
       </c>
       <c r="I103" s="14">
-        <f>SUM(I94:I102)</f>
+        <f>SUM(I100:I102)</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>EXISTING MACHINE PARTS (reuse, check they work)</t>
+          <t>WIRING + ENCLOSURE</t>
         </is>
       </c>
       <c r="B104" s="5" t="n"/>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Oil pressure switch</t>
+          <t>Enclosure</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Original, closes on low pressure</t>
+          <t>IP65+, fits Pi + interface boards</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Sch. 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>GPIO 22 via optocoupler</t>
+          <t>Vibration-mount it</t>
         </is>
       </c>
       <c r="H105" s="9" t="n"/>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Hydraulic filter bypass switch</t>
+          <t>Prototype board</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Original, closes on bypass</t>
+          <t>Perfboard / stripboard</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Sch. 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>ADS1115 A2, monitored (4.7k EOL resistor at the switch)</t>
+          <t>Only if hand-wiring instead of the breakout board</t>
         </is>
       </c>
       <c r="H106" s="9" t="n"/>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Hydraulic oil temp switch</t>
+          <t>Automotive wire</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Original, closes when hot</t>
+          <t>18 AWG TXL/GXL, several colors</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Sch. 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>ADS1115 A3, monitored (4.7k EOL resistor at the switch)</t>
+          <t>Lot</t>
         </is>
       </c>
       <c r="H107" s="9" t="n"/>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Fuel sender</t>
+          <t>Sealed connectors</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Original, in tank</t>
+          <t>Deutsch DT or Weatherpack assortment</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Sch. 4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Calibrate with dash.py --calibrate</t>
+          <t>Avoid loose Dupont jumpers on the machine</t>
         </is>
       </c>
       <c r="H108" s="9" t="n"/>
@@ -4161,52 +4161,440 @@
       <c r="K108" s="12" t="n"/>
     </row>
     <row r="109">
-      <c r="G109" s="13" t="inlineStr">
+      <c r="A109" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Screw terminal blocks</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>PCB 5 mm pitch assortment</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>Field wiring into the enclosure</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="n"/>
+      <c r="I109" s="10">
+        <f>B109*H109</f>
+        <v/>
+      </c>
+      <c r="J109" s="11" t="n"/>
+      <c r="K109" s="12" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Heat-shrink + terminals</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Assortment</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="n"/>
+      <c r="I110" s="10">
+        <f>B110*H110</f>
+        <v/>
+      </c>
+      <c r="J110" s="11" t="n"/>
+      <c r="K110" s="12" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B111" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Display mount</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>RAM-style ball mount or bracket</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>With vibration damping</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="n"/>
+      <c r="I111" s="10">
+        <f>B111*H111</f>
+        <v/>
+      </c>
+      <c r="J111" s="11" t="n"/>
+      <c r="K111" s="12" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Standoffs</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>M2.5 nylon/brass set</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>Mount the Pi and the plug-in modules</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="n"/>
+      <c r="I112" s="10">
+        <f>B112*H112</f>
+        <v/>
+      </c>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="12" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B113" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>M3 standoff + screws</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>10 mm or taller, all the same height</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Board README</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>Breakout board mounting: 4 corners, 4 mid-sides, 1 centre (drilling template)</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="n"/>
+      <c r="I113" s="10">
+        <f>B113*H113</f>
+        <v/>
+      </c>
+      <c r="J113" s="11" t="n"/>
+      <c r="K113" s="12" t="n"/>
+    </row>
+    <row r="114">
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>Subtotal — Wiring + Enclosure</t>
+        </is>
+      </c>
+      <c r="I114" s="14">
+        <f>SUM(I105:I113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>EXISTING MACHINE PARTS (reuse, check they work)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="5" t="n"/>
+      <c r="I115" s="5" t="n"/>
+      <c r="J115" s="5" t="n"/>
+      <c r="K115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B116" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Oil pressure switch</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>Original, closes on low pressure</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 5</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>GPIO 22 via optocoupler</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="n"/>
+      <c r="I116" s="10">
+        <f>B116*H116</f>
+        <v/>
+      </c>
+      <c r="J116" s="11" t="n"/>
+      <c r="K116" s="12" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B117" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Hydraulic filter bypass switch</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>Original, closes on bypass</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 5</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>ADS1115 A2, monitored (4.7k EOL resistor at the switch)</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="n"/>
+      <c r="I117" s="10">
+        <f>B117*H117</f>
+        <v/>
+      </c>
+      <c r="J117" s="11" t="n"/>
+      <c r="K117" s="12" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B118" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Hydraulic oil temp switch</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>Original, closes when hot</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 5</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>ADS1115 A3, monitored (4.7k EOL resistor at the switch)</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="n"/>
+      <c r="I118" s="10">
+        <f>B118*H118</f>
+        <v/>
+      </c>
+      <c r="J118" s="11" t="n"/>
+      <c r="K118" s="12" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B119" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Fuel sender</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>Original, in tank</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 4</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>Calibrate with dash.py --calibrate</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="n"/>
+      <c r="I119" s="10">
+        <f>B119*H119</f>
+        <v/>
+      </c>
+      <c r="J119" s="11" t="n"/>
+      <c r="K119" s="12" t="n"/>
+    </row>
+    <row r="120">
+      <c r="G120" s="13" t="inlineStr">
         <is>
           <t>Subtotal — Existing Machine Parts</t>
         </is>
       </c>
-      <c r="I109" s="14">
-        <f>SUM(I105:I108)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="G111" s="15" t="inlineStr">
+      <c r="I120" s="14">
+        <f>SUM(I116:I119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="G122" s="15" t="inlineStr">
         <is>
           <t>TOTAL (all sections)</t>
         </is>
       </c>
-      <c r="I111" s="16">
-        <f>I14+I20+I34+I40+I51+I59+I68+I74+I87+I92+I103+I109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="G112" s="17" t="inlineStr">
+      <c r="I122" s="16">
+        <f>I14+I20+I34+I40+I51+I59+I68+I74+I87+I98+I103+I114+I120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="G123" s="17" t="inlineStr">
         <is>
           <t>Items still to order (excl. existing parts)</t>
         </is>
       </c>
-      <c r="I112" s="18">
-        <f>COUNTIF(B6:B103,"&gt;0")-COUNTIF(K6:K103,"Y")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="19" t="inlineStr">
+      <c r="I123" s="18">
+        <f>COUNTIF(B6:B114,"&gt;0")-COUNTIF(K6:K114,"Y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>Notes: Qty in blue = quantity per machine. Existing machine parts usually cost $0 unless one needs replacing. Prices are left blank on purpose. Enter what you actually pay.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K109"/>
+  <autoFilter ref="A5:K120"/>
   <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K13 K16 K17 K18 K19 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K36 K37 K38 K39 K42 K43 K44 K45 K46 K47 K48 K49 K50 K53 K54 K55 K56 K57 K58 K61 K62 K63 K64 K65 K66 K67 K70 K71 K72 K73 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K89 K90 K91 K94 K95 K96 K97 K98 K99 K100 K101 K102 K105 K106 K107 K108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K13 K16 K17 K18 K19 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K36 K37 K38 K39 K42 K43 K44 K45 K46 K47 K48 K49 K50 K53 K54 K55 K56 K57 K58 K61 K62 K63 K64 K65 K66 K67 K70 K71 K72 K73 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K89 K90 K91 K92 K93 K94 K95 K96 K97 K100 K101 K102 K105 K106 K107 K108 K109 K110 K111 K112 K113 K116 K117 K118 K119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
